--- a/output/2026-summer_日別人数表.xlsx
+++ b/output/2026-summer_日別人数表.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46256</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="4">
